--- a/AAII_Financials/Quarterly/CSPCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CSPCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="92">
   <si>
     <t>CSPCY</t>
   </si>
@@ -656,84 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -779,8 +783,11 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -826,8 +833,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -873,8 +883,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +905,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -939,8 +953,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,8 +1003,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1033,8 +1053,11 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,8 +1122,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1143,8 +1170,11 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1190,8 +1220,11 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,8 +1242,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1256,8 +1290,11 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1303,8 +1340,11 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1350,8 +1390,11 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1397,8 +1440,11 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1444,8 +1490,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,8 +1540,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1538,8 +1590,11 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1585,8 +1640,11 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,8 +1840,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1820,8 +1890,11 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1867,8 +1940,11 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,8 +1990,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1961,60 +2040,66 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,201 +2137,214 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="3">
+        <v>1423000</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" s="3">
         <v>870600</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3">
         <v>928500</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L41" s="3">
         <v>1152400</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N41" s="3">
         <v>1694500</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P41" s="3">
         <v>1258900</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R41" s="3">
         <v>1493100</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1288900</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>612400</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>1354500</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>323400</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>336100</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>246800</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>499200</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>618800</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D43" s="3">
+        <v>1314200</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3">
         <v>1256300</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3">
         <v>1375300</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>1318100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3">
         <v>1677500</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3">
         <v>1387900</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
         <v>1224400</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R43" s="3">
         <v>991200</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E44" s="3">
+      <c r="D44" s="3">
+        <v>472500</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>441900</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3">
         <v>426300</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>428800</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>476000</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>442600</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>379500</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3">
         <v>370400</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>43700</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
@@ -2286,196 +2385,211 @@
       <c r="Q45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E46" s="3">
+      <c r="D46" s="3">
+        <v>4542300</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" s="3">
         <v>3181200</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="3">
         <v>3156200</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3">
         <v>2998700</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="3">
         <v>3642000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N46" s="3">
         <v>3771700</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P46" s="3">
         <v>3361900</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R46" s="3">
         <v>3473500</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3">
+        <v>1103000</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3">
         <v>1016300</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3">
         <v>923200</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3">
         <v>859100</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3">
         <v>887000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>648100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3">
         <v>642300</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R47" s="3">
         <v>539400</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E48" s="3">
+      <c r="D48" s="3">
+        <v>2007800</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3">
         <v>1928600</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3">
         <v>1816700</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3">
         <v>1712900</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3">
         <v>1601200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N48" s="3">
         <v>1641900</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3">
         <v>1566200</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R48" s="3">
         <v>1591500</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>474200</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>413600</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>403500</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>377100</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>340600</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>335800</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>344600</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
       <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
         <v>305500</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,55 +2685,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3">
         <v>89800</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3">
         <v>93600</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
         <v>86600</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3">
         <v>90400</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3">
         <v>95700</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3">
         <v>86800</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R52" s="3">
         <v>124600</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2785,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E54" s="3">
+      <c r="D54" s="3">
+        <v>8247200</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54" s="3">
         <v>6676500</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3">
         <v>6421500</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3">
         <v>6081400</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3">
         <v>6591000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N54" s="3">
         <v>6527000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P54" s="3">
         <v>6022000</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R54" s="3">
         <v>6056000</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,243 +2877,259 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="D57" s="3">
+        <v>441500</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3">
         <v>487400</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3">
         <v>376100</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3">
         <v>409400</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3">
         <v>444500</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>407400</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P57" s="3">
         <v>340500</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R57" s="3">
         <v>319800</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>38800</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>65800</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>46900</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>61800</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>44400</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>84600</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>28700</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3">
+        <v>1019200</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
         <v>385300</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3">
         <v>988500</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
         <v>325100</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>945900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>944000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>293700</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>367500</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E60" s="3">
+      <c r="D60" s="3">
+        <v>2123500</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="3">
         <v>1455100</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3">
         <v>1411600</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3">
         <v>1319900</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3">
         <v>1436000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" s="3">
         <v>1436000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P60" s="3">
         <v>1244500</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R60" s="3">
         <v>1298800</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>57300</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>25800</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>22200</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>7700</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>9100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>15100</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>28500</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3008,18 +3154,18 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>48200</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>8300</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3029,8 +3175,11 @@
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3325,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E66" s="3">
+      <c r="D66" s="3">
+        <v>2442400</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="3">
         <v>1736800</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3">
         <v>1554800</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3">
         <v>1441600</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3">
         <v>1572100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N66" s="3">
         <v>1588500</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P66" s="3">
         <v>1401100</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R66" s="3">
         <v>1468400</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3595,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3">
+        <v>4635000</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
         <v>3841700</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>3743400</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>3514100</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>3752600</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>3701200</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>3439400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>3362500</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3795,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5538800</v>
+      </c>
+      <c r="E76" s="3">
         <v>4810200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4743500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4670400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4641300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4446300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4420400</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3">
         <v>4795900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4598500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4682500</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P76" s="3">
         <v>4387500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4396100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4378200</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,60 +3895,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3805,8 +4000,11 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,8 +4022,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3871,8 +4070,11 @@
       <c r="Q83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,8 +4320,11 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4153,8 +4370,11 @@
       <c r="Q89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,8 +4392,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4219,8 +4440,11 @@
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,8 +4540,11 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4360,8 +4590,11 @@
       <c r="Q94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4612,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,8 +4810,11 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4614,8 +4860,11 @@
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4661,8 +4910,11 @@
       <c r="Q101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4706,6 +4958,9 @@
         <v>4</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
